--- a/DataEngineering training plan - Aug 2024 Batch 2.xlsx
+++ b/DataEngineering training plan - Aug 2024 Batch 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sudha G\Data Engineering\Aug 2024 Batch\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rajesh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027C7A0B-7286-4B62-88B7-725784CB058D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700CB5D2-8848-4084-BFCA-644052AE6B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{62AC6C7A-AEF2-44F7-A87A-FD4461E9C886}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{62AC6C7A-AEF2-44F7-A87A-FD4461E9C886}"/>
   </bookViews>
   <sheets>
     <sheet name="Weekly Schedule" sheetId="6" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Evaluation Criteria'!$A$1:$F$19</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,6 +31,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="123">
   <si>
     <t>Topics</t>
   </si>
@@ -468,12 +470,6 @@
   </si>
   <si>
     <t>Detail Topics</t>
-  </si>
-  <si>
-    <t>Start Date</t>
-  </si>
-  <si>
-    <t>End Date</t>
   </si>
   <si>
     <t>SQL Coding Assessment &amp; Evaluation</t>
@@ -687,19 +683,13 @@
     <t>Project 2 - Throughout the training</t>
   </si>
   <si>
-    <t>No Training on 22nd August. Break has been  provided for the participants to complete the assignment and prepare for Coding assignment. Participants have to do this activity on their own. Trainer and participants don’t have to join the Teams link on this specific day.</t>
-  </si>
-  <si>
-    <t>No Training on 29th August. Break has been  provided for the participants to complete the assignment and prepare for Coding assignment. Participants have to do this activity on their own. Trainer and participants don’t have to join the Teams link on this specific day.</t>
-  </si>
-  <si>
-    <t>No Training on 6th September and 09th September. Break has been  provided for the participants to complete the assignment and prepare for Coding assignment. Participants have to do this activity on their own. Trainer and participants don’t have to join the Teams link on this specific days.</t>
-  </si>
-  <si>
-    <t>No Training on 19th and 20rd September. Break has been  provided for the participants to complete the assignment and prepare for Coding assignment. Participants have to do this activity on their own. Trainer and participants don’t have to join the Teams link on this specific days.</t>
-  </si>
-  <si>
-    <t>No Training on 1st and 3rd October. Break has been  provided for the participants to complete the assignment and prepare for Coding assignment. Participants have to do this activity on their own. Trainer and participants don’t have to join the Teams link on this specific days.</t>
+    <t>Additional Days</t>
+  </si>
+  <si>
+    <t>1 Day</t>
+  </si>
+  <si>
+    <t>2 Day</t>
   </si>
 </sst>
 </file>
@@ -707,9 +697,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -754,6 +744,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -868,7 +866,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -930,12 +928,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -947,54 +945,57 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1014,9 +1015,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1054,7 +1055,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1160,7 +1161,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1302,7 +1303,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1310,20 +1311,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7486C18-6BB6-450D-B91B-F71160628768}">
-  <dimension ref="A1:G58"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H58"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" style="4" customWidth="1"/>
-    <col min="2" max="2" width="63.85546875" style="17" customWidth="1"/>
-    <col min="3" max="3" width="91.7109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="27" style="49" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.140625" style="49" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.140625" style="4" customWidth="1"/>
-    <col min="8" max="16384" width="8.7109375" style="4"/>
+    <col min="2" max="2" width="63.88671875" style="17" customWidth="1"/>
+    <col min="3" max="3" width="91.5546875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="27" style="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.109375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="8.5546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>76</v>
       </c>
@@ -1333,21 +1335,20 @@
       <c r="C1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="44" t="s">
-        <v>79</v>
-      </c>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
       <c r="F1" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="102" x14ac:dyDescent="0.2">
-      <c r="A2" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1356,21 +1357,18 @@
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="45">
-        <v>45523</v>
-      </c>
-      <c r="E2" s="45">
-        <v>45527</v>
-      </c>
-      <c r="F2" s="36">
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="42">
         <v>4</v>
       </c>
-      <c r="G2" s="40" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="36"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="50" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="42"/>
       <c r="B3" s="5" t="s">
         <v>71</v>
       </c>
@@ -1379,11 +1377,12 @@
       </c>
       <c r="D3" s="45"/>
       <c r="E3" s="45"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="40"/>
-    </row>
-    <row r="4" spans="1:7" ht="204" x14ac:dyDescent="0.2">
-      <c r="A4" s="36"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="50"/>
+    </row>
+    <row r="4" spans="1:8" ht="220.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="42"/>
       <c r="B4" s="7" t="s">
         <v>49</v>
       </c>
@@ -1392,11 +1391,12 @@
       </c>
       <c r="D4" s="45"/>
       <c r="E4" s="45"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="40"/>
-    </row>
-    <row r="5" spans="1:7" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="36"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="50"/>
+    </row>
+    <row r="5" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="42"/>
       <c r="B5" s="7" t="s">
         <v>50</v>
       </c>
@@ -1405,11 +1405,12 @@
       </c>
       <c r="D5" s="45"/>
       <c r="E5" s="45"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="40"/>
-    </row>
-    <row r="6" spans="1:7" ht="102" x14ac:dyDescent="0.2">
-      <c r="A6" s="36"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="50"/>
+    </row>
+    <row r="6" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="42"/>
       <c r="B6" s="7" t="s">
         <v>51</v>
       </c>
@@ -1418,37 +1419,40 @@
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="40"/>
-    </row>
-    <row r="7" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A7" s="36"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="50"/>
+    </row>
+    <row r="7" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="42"/>
       <c r="B7" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="40"/>
-    </row>
-    <row r="8" spans="1:7" ht="178.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="36"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="50"/>
+    </row>
+    <row r="8" spans="1:8" ht="193.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="42"/>
       <c r="B8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D8" s="45"/>
       <c r="E8" s="45"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="40"/>
-    </row>
-    <row r="9" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A9" s="36"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="50"/>
+    </row>
+    <row r="9" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="42"/>
       <c r="B9" s="7" t="s">
         <v>9</v>
       </c>
@@ -1457,33 +1461,36 @@
       </c>
       <c r="D9" s="45"/>
       <c r="E9" s="45"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="40"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="36"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="50"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="42"/>
       <c r="B10" s="18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="45"/>
       <c r="E10" s="45"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="40"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="36"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="50"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="42"/>
       <c r="B11" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="45"/>
       <c r="E11" s="45"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="40"/>
-    </row>
-    <row r="12" spans="1:7" ht="114.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="37" t="s">
+      <c r="F11" s="42"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="50"/>
+    </row>
+    <row r="12" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="43" t="s">
         <v>2</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -1492,21 +1499,18 @@
       <c r="C12" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="46">
-        <v>45530</v>
-      </c>
-      <c r="E12" s="46">
-        <v>45534</v>
-      </c>
-      <c r="F12" s="37">
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="43">
         <v>4</v>
       </c>
-      <c r="G12" s="41" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="178.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="37"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="50" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="193.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="43"/>
       <c r="B13" s="9" t="s">
         <v>60</v>
       </c>
@@ -1515,11 +1519,12 @@
       </c>
       <c r="D13" s="46"/>
       <c r="E13" s="46"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="42"/>
-    </row>
-    <row r="14" spans="1:7" ht="127.5" x14ac:dyDescent="0.2">
-      <c r="A14" s="37"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="50"/>
+    </row>
+    <row r="14" spans="1:8" ht="138" x14ac:dyDescent="0.3">
+      <c r="A14" s="43"/>
       <c r="B14" s="9" t="s">
         <v>62</v>
       </c>
@@ -1528,11 +1533,12 @@
       </c>
       <c r="D14" s="46"/>
       <c r="E14" s="46"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="42"/>
-    </row>
-    <row r="15" spans="1:7" ht="114.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="37"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="50"/>
+    </row>
+    <row r="15" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="43"/>
       <c r="B15" s="9" t="s">
         <v>64</v>
       </c>
@@ -1541,11 +1547,12 @@
       </c>
       <c r="D15" s="46"/>
       <c r="E15" s="46"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="42"/>
-    </row>
-    <row r="16" spans="1:7" ht="102" x14ac:dyDescent="0.2">
-      <c r="A16" s="37"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="50"/>
+    </row>
+    <row r="16" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="43"/>
       <c r="B16" s="9" t="s">
         <v>65</v>
       </c>
@@ -1554,11 +1561,12 @@
       </c>
       <c r="D16" s="46"/>
       <c r="E16" s="46"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="42"/>
-    </row>
-    <row r="17" spans="1:7" ht="216.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="37"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="50"/>
+    </row>
+    <row r="17" spans="1:8" ht="234.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="43"/>
       <c r="B17" s="9" t="s">
         <v>67</v>
       </c>
@@ -1567,11 +1575,12 @@
       </c>
       <c r="D17" s="46"/>
       <c r="E17" s="46"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="42"/>
-    </row>
-    <row r="18" spans="1:7" ht="153" x14ac:dyDescent="0.2">
-      <c r="A18" s="37"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="50"/>
+    </row>
+    <row r="18" spans="1:8" ht="165.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="43"/>
       <c r="B18" s="9" t="s">
         <v>68</v>
       </c>
@@ -1580,11 +1589,12 @@
       </c>
       <c r="D18" s="46"/>
       <c r="E18" s="46"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="42"/>
-    </row>
-    <row r="19" spans="1:7" ht="102" x14ac:dyDescent="0.2">
-      <c r="A19" s="37"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="50"/>
+    </row>
+    <row r="19" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="43"/>
       <c r="B19" s="9" t="s">
         <v>74</v>
       </c>
@@ -1593,33 +1603,36 @@
       </c>
       <c r="D19" s="46"/>
       <c r="E19" s="46"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="42"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="37"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="50"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="43"/>
       <c r="B20" s="18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="46"/>
       <c r="E20" s="46"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="42"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="37"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="50"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="43"/>
       <c r="B21" s="11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="46"/>
       <c r="E21" s="46"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="43"/>
-    </row>
-    <row r="22" spans="1:7" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A22" s="38" t="s">
+      <c r="F21" s="43"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="50"/>
+    </row>
+    <row r="22" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="44" t="s">
         <v>3</v>
       </c>
       <c r="B22" s="12" t="s">
@@ -1628,22 +1641,19 @@
       <c r="C22" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="47">
-        <v>45537</v>
-      </c>
-      <c r="E22" s="47">
-        <v>45545</v>
-      </c>
-      <c r="F22" s="38">
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="44">
         <v>5</v>
       </c>
-      <c r="G22" s="39" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A23" s="38"/>
-      <c r="B23" s="34" t="s">
+      <c r="G22" s="37"/>
+      <c r="H22" s="50" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="44"/>
+      <c r="B23" s="48" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="13" t="s">
@@ -1651,133 +1661,140 @@
       </c>
       <c r="D23" s="47"/>
       <c r="E23" s="47"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="39"/>
-    </row>
-    <row r="24" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A24" s="38"/>
-      <c r="B24" s="34"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="50"/>
+    </row>
+    <row r="24" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="44"/>
+      <c r="B24" s="48"/>
       <c r="C24" s="13" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="47"/>
       <c r="E24" s="47"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="39"/>
-    </row>
-    <row r="25" spans="1:7" ht="140.25" x14ac:dyDescent="0.2">
-      <c r="A25" s="38"/>
-      <c r="B25" s="34"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="50"/>
+    </row>
+    <row r="25" spans="1:8" ht="151.80000000000001" x14ac:dyDescent="0.3">
+      <c r="A25" s="44"/>
+      <c r="B25" s="48"/>
       <c r="C25" s="13" t="s">
         <v>20</v>
       </c>
       <c r="D25" s="47"/>
       <c r="E25" s="47"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="39"/>
-    </row>
-    <row r="26" spans="1:7" ht="114.75" x14ac:dyDescent="0.2">
-      <c r="A26" s="38"/>
-      <c r="B26" s="34"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="50"/>
+    </row>
+    <row r="26" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="44"/>
+      <c r="B26" s="48"/>
       <c r="C26" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D26" s="47"/>
       <c r="E26" s="47"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="39"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="38"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="50"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="44"/>
       <c r="B27" s="19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="47"/>
       <c r="E27" s="47"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="39"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="38"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="50"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="44"/>
       <c r="B28" s="11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="47"/>
       <c r="E28" s="47"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="39"/>
-    </row>
-    <row r="29" spans="1:7" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="37" t="s">
+      <c r="F28" s="44"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="50"/>
+    </row>
+    <row r="29" spans="1:8" ht="69" x14ac:dyDescent="0.3">
+      <c r="A29" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B29" s="35" t="s">
+      <c r="B29" s="49" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="46">
-        <v>45546</v>
-      </c>
-      <c r="E29" s="46">
-        <v>45558</v>
-      </c>
-      <c r="F29" s="37">
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="43">
         <v>7</v>
       </c>
-      <c r="G29" s="39" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A30" s="37"/>
-      <c r="B30" s="35"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="50" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="43"/>
+      <c r="B30" s="49"/>
       <c r="C30" s="10" t="s">
         <v>13</v>
       </c>
       <c r="D30" s="46"/>
       <c r="E30" s="46"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="39"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="37"/>
-      <c r="B31" s="35"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="50"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="43"/>
+      <c r="B31" s="49"/>
       <c r="C31" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D31" s="46"/>
       <c r="E31" s="46"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="39"/>
-    </row>
-    <row r="32" spans="1:7" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A32" s="37"/>
-      <c r="B32" s="35"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="50"/>
+    </row>
+    <row r="32" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="43"/>
+      <c r="B32" s="49"/>
       <c r="C32" s="10" t="s">
         <v>22</v>
       </c>
       <c r="D32" s="46"/>
       <c r="E32" s="46"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="39"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="37"/>
-      <c r="B33" s="35"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="50"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="43"/>
+      <c r="B33" s="49"/>
       <c r="C33" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D33" s="46"/>
       <c r="E33" s="46"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="39"/>
-    </row>
-    <row r="34" spans="1:7" ht="114.75" x14ac:dyDescent="0.2">
-      <c r="A34" s="37"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="50"/>
+    </row>
+    <row r="34" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="43"/>
       <c r="B34" s="9" t="s">
         <v>12</v>
       </c>
@@ -1786,11 +1803,12 @@
       </c>
       <c r="D34" s="46"/>
       <c r="E34" s="46"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="39"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="37"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="50"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="43"/>
       <c r="B35" s="14" t="s">
         <v>25</v>
       </c>
@@ -1799,11 +1817,12 @@
       </c>
       <c r="D35" s="46"/>
       <c r="E35" s="46"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="39"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="37"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="50"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="43"/>
       <c r="B36" s="9" t="s">
         <v>26</v>
       </c>
@@ -1812,11 +1831,12 @@
       </c>
       <c r="D36" s="46"/>
       <c r="E36" s="46"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="39"/>
-    </row>
-    <row r="37" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A37" s="37"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="50"/>
+    </row>
+    <row r="37" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="43"/>
       <c r="B37" s="14" t="s">
         <v>28</v>
       </c>
@@ -1825,11 +1845,12 @@
       </c>
       <c r="D37" s="46"/>
       <c r="E37" s="46"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="39"/>
-    </row>
-    <row r="38" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A38" s="37"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="50"/>
+    </row>
+    <row r="38" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="43"/>
       <c r="B38" s="14" t="s">
         <v>31</v>
       </c>
@@ -1838,11 +1859,12 @@
       </c>
       <c r="D38" s="46"/>
       <c r="E38" s="46"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="39"/>
-    </row>
-    <row r="39" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A39" s="37"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="37"/>
+      <c r="H38" s="50"/>
+    </row>
+    <row r="39" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A39" s="43"/>
       <c r="B39" s="14" t="s">
         <v>33</v>
       </c>
@@ -1851,11 +1873,12 @@
       </c>
       <c r="D39" s="46"/>
       <c r="E39" s="46"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="39"/>
-    </row>
-    <row r="40" spans="1:7" ht="127.5" x14ac:dyDescent="0.2">
-      <c r="A40" s="37"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="37"/>
+      <c r="H39" s="50"/>
+    </row>
+    <row r="40" spans="1:8" ht="138" x14ac:dyDescent="0.3">
+      <c r="A40" s="43"/>
       <c r="B40" s="14" t="s">
         <v>35</v>
       </c>
@@ -1864,11 +1887,12 @@
       </c>
       <c r="D40" s="46"/>
       <c r="E40" s="46"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="39"/>
-    </row>
-    <row r="41" spans="1:7" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A41" s="37"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="37"/>
+      <c r="H40" s="50"/>
+    </row>
+    <row r="41" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="43"/>
       <c r="B41" s="14" t="s">
         <v>39</v>
       </c>
@@ -1877,11 +1901,12 @@
       </c>
       <c r="D41" s="46"/>
       <c r="E41" s="46"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="39"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="37"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="50"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="43"/>
       <c r="B42" s="14" t="s">
         <v>36</v>
       </c>
@@ -1890,11 +1915,12 @@
       </c>
       <c r="D42" s="46"/>
       <c r="E42" s="46"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="39"/>
-    </row>
-    <row r="43" spans="1:7" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A43" s="37"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="50"/>
+    </row>
+    <row r="43" spans="1:8" ht="69" x14ac:dyDescent="0.3">
+      <c r="A43" s="43"/>
       <c r="B43" s="14" t="s">
         <v>41</v>
       </c>
@@ -1903,208 +1929,204 @@
       </c>
       <c r="D43" s="46"/>
       <c r="E43" s="46"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="39"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" s="37"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="50"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="43"/>
       <c r="B44" s="20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C44" s="10"/>
       <c r="D44" s="46"/>
       <c r="E44" s="46"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="39"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="37"/>
+      <c r="F44" s="43"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="50"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="43"/>
       <c r="B45" s="15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="46"/>
       <c r="E45" s="46"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="39"/>
-    </row>
-    <row r="46" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A46" s="38" t="s">
+      <c r="F45" s="43"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="50"/>
+    </row>
+    <row r="46" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A46" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B46" s="34" t="s">
+      <c r="B46" s="48" t="s">
         <v>5</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D46" s="47">
-        <v>45559</v>
-      </c>
-      <c r="E46" s="47">
-        <v>45569</v>
-      </c>
-      <c r="F46" s="38">
+        <v>85</v>
+      </c>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="44">
         <v>6</v>
       </c>
-      <c r="G46" s="39" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A47" s="38"/>
-      <c r="B47" s="34"/>
+      <c r="G46" s="37"/>
+      <c r="H46" s="50" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="69" x14ac:dyDescent="0.3">
+      <c r="A47" s="44"/>
+      <c r="B47" s="48"/>
       <c r="C47" s="13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D47" s="47"/>
       <c r="E47" s="47"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="39"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="38"/>
-      <c r="B48" s="34"/>
+      <c r="F47" s="44"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="50"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="44"/>
+      <c r="B48" s="48"/>
       <c r="C48" s="13" t="s">
         <v>44</v>
       </c>
       <c r="D48" s="47"/>
       <c r="E48" s="47"/>
-      <c r="F48" s="38"/>
-      <c r="G48" s="39"/>
-    </row>
-    <row r="49" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A49" s="38"/>
-      <c r="B49" s="34"/>
+      <c r="F48" s="44"/>
+      <c r="G48" s="37"/>
+      <c r="H48" s="50"/>
+    </row>
+    <row r="49" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A49" s="44"/>
+      <c r="B49" s="48"/>
       <c r="C49" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D49" s="47"/>
       <c r="E49" s="47"/>
-      <c r="F49" s="38"/>
-      <c r="G49" s="39"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" s="38"/>
-      <c r="B50" s="34"/>
+      <c r="F49" s="44"/>
+      <c r="G49" s="37"/>
+      <c r="H49" s="50"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="44"/>
+      <c r="B50" s="48"/>
       <c r="C50" s="13" t="s">
         <v>43</v>
       </c>
       <c r="D50" s="47"/>
       <c r="E50" s="47"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="39"/>
-    </row>
-    <row r="51" spans="1:7" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A51" s="38"/>
-      <c r="B51" s="34"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="37"/>
+      <c r="H50" s="50"/>
+    </row>
+    <row r="51" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="44"/>
+      <c r="B51" s="48"/>
       <c r="C51" s="13" t="s">
         <v>45</v>
       </c>
       <c r="D51" s="47"/>
       <c r="E51" s="47"/>
-      <c r="F51" s="38"/>
-      <c r="G51" s="39"/>
-    </row>
-    <row r="52" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A52" s="38"/>
-      <c r="B52" s="34"/>
+      <c r="F51" s="44"/>
+      <c r="G51" s="37"/>
+      <c r="H51" s="50"/>
+    </row>
+    <row r="52" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="44"/>
+      <c r="B52" s="48"/>
       <c r="C52" s="13" t="s">
         <v>46</v>
       </c>
       <c r="D52" s="47"/>
       <c r="E52" s="47"/>
-      <c r="F52" s="38"/>
-      <c r="G52" s="39"/>
-    </row>
-    <row r="53" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A53" s="38"/>
-      <c r="B53" s="34"/>
+      <c r="F52" s="44"/>
+      <c r="G52" s="37"/>
+      <c r="H52" s="50"/>
+    </row>
+    <row r="53" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A53" s="44"/>
+      <c r="B53" s="48"/>
       <c r="C53" s="13" t="s">
         <v>47</v>
       </c>
       <c r="D53" s="47"/>
       <c r="E53" s="47"/>
-      <c r="F53" s="38"/>
-      <c r="G53" s="39"/>
-    </row>
-    <row r="54" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A54" s="38"/>
-      <c r="B54" s="34"/>
+      <c r="F53" s="44"/>
+      <c r="G53" s="37"/>
+      <c r="H53" s="50"/>
+    </row>
+    <row r="54" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="44"/>
+      <c r="B54" s="48"/>
       <c r="C54" s="13" t="s">
         <v>48</v>
       </c>
       <c r="D54" s="47"/>
       <c r="E54" s="47"/>
-      <c r="F54" s="38"/>
-      <c r="G54" s="39"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" s="38"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="37"/>
+      <c r="H54" s="50"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="44"/>
       <c r="B55" s="19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C55" s="13"/>
       <c r="D55" s="47"/>
       <c r="E55" s="47"/>
-      <c r="F55" s="38"/>
-      <c r="G55" s="39"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56" s="38"/>
+      <c r="F55" s="44"/>
+      <c r="G55" s="37"/>
+      <c r="H55" s="50"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="44"/>
       <c r="B56" s="11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C56" s="16"/>
       <c r="D56" s="47"/>
       <c r="E56" s="47"/>
-      <c r="F56" s="38"/>
-      <c r="G56" s="39"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F56" s="44"/>
+      <c r="G56" s="37"/>
+      <c r="H56" s="50"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="21"/>
       <c r="B57" s="22" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C57" s="21"/>
-      <c r="D57" s="48"/>
-      <c r="E57" s="48"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
       <c r="F57" s="23"/>
       <c r="G57" s="24"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H57" s="23"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="21"/>
       <c r="B58" s="22" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C58" s="21"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="48"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
       <c r="F58" s="23"/>
       <c r="G58" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="G46:G56"/>
-    <mergeCell ref="G2:G11"/>
-    <mergeCell ref="G12:G21"/>
-    <mergeCell ref="G22:G28"/>
-    <mergeCell ref="G29:G45"/>
-    <mergeCell ref="F2:F11"/>
-    <mergeCell ref="F12:F21"/>
-    <mergeCell ref="F22:F28"/>
-    <mergeCell ref="F29:F45"/>
-    <mergeCell ref="F46:F56"/>
-    <mergeCell ref="D2:D11"/>
-    <mergeCell ref="D12:D21"/>
-    <mergeCell ref="D22:D28"/>
-    <mergeCell ref="D29:D45"/>
-    <mergeCell ref="D46:D56"/>
-    <mergeCell ref="E2:E11"/>
-    <mergeCell ref="E12:E21"/>
-    <mergeCell ref="E22:E28"/>
-    <mergeCell ref="E29:E45"/>
-    <mergeCell ref="E46:E56"/>
+  <mergeCells count="33">
+    <mergeCell ref="H2:H11"/>
+    <mergeCell ref="H12:H21"/>
+    <mergeCell ref="H22:H28"/>
+    <mergeCell ref="H46:H56"/>
+    <mergeCell ref="H29:H45"/>
     <mergeCell ref="B23:B26"/>
     <mergeCell ref="B29:B33"/>
     <mergeCell ref="B46:B54"/>
@@ -2113,6 +2135,26 @@
     <mergeCell ref="A22:A28"/>
     <mergeCell ref="A29:A45"/>
     <mergeCell ref="A46:A56"/>
+    <mergeCell ref="E2:E11"/>
+    <mergeCell ref="E12:E21"/>
+    <mergeCell ref="E22:E28"/>
+    <mergeCell ref="E29:E45"/>
+    <mergeCell ref="E46:E56"/>
+    <mergeCell ref="D2:D11"/>
+    <mergeCell ref="D12:D21"/>
+    <mergeCell ref="D22:D28"/>
+    <mergeCell ref="D29:D45"/>
+    <mergeCell ref="D46:D56"/>
+    <mergeCell ref="F2:F11"/>
+    <mergeCell ref="F12:F21"/>
+    <mergeCell ref="F22:F28"/>
+    <mergeCell ref="F29:F45"/>
+    <mergeCell ref="F46:F56"/>
+    <mergeCell ref="G46:G56"/>
+    <mergeCell ref="G2:G11"/>
+    <mergeCell ref="G12:G21"/>
+    <mergeCell ref="G22:G28"/>
+    <mergeCell ref="G29:G45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2121,64 +2163,64 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{327668D7-320B-44CB-87F3-432207E3B904}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.42578125" style="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.44140625" style="32" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C1" s="25"/>
       <c r="D1" s="1"/>
       <c r="E1" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="C2" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="E2" s="26" t="s">
         <v>101</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>103</v>
       </c>
       <c r="F2" s="27">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C3" s="28">
         <v>45531</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E3" s="26">
         <v>1</v>
@@ -2187,18 +2229,18 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C4" s="28">
         <v>45533</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E4" s="26">
         <v>1</v>
@@ -2207,12 +2249,12 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="29" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C5" s="28">
         <v>45527</v>
@@ -2225,18 +2267,18 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="29" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C6" s="28">
         <v>45538</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E6" s="26">
         <v>1</v>
@@ -2245,18 +2287,18 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C7" s="28">
         <v>45540</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E7" s="26">
         <v>1</v>
@@ -2265,12 +2307,12 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C8" s="28">
         <v>45534</v>
@@ -2283,18 +2325,18 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C9" s="28">
         <v>45547</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E9" s="26">
         <v>1</v>
@@ -2303,18 +2345,18 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C10" s="28">
         <v>45552</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E10" s="26">
         <v>1</v>
@@ -2323,12 +2365,12 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="30" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C11" s="28">
         <v>45545</v>
@@ -2341,18 +2383,18 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="30" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C12" s="28">
         <v>45560</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E12" s="26">
         <v>1</v>
@@ -2361,18 +2403,18 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="30" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C13" s="28">
         <v>45562</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E13" s="26">
         <v>1</v>
@@ -2381,12 +2423,12 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="31" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C14" s="28">
         <v>45558</v>
@@ -2399,18 +2441,18 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="31" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C15" s="28">
         <v>45573</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E15" s="26">
         <v>1</v>
@@ -2419,18 +2461,18 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="31" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C16" s="28">
         <v>45575</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E16" s="26">
         <v>1</v>
@@ -2439,12 +2481,12 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="30" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C17" s="28">
         <v>45569</v>
@@ -2457,9 +2499,9 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="30" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="28">
@@ -2467,15 +2509,15 @@
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F18" s="27">
         <v>0.75</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="28">
@@ -2483,7 +2525,7 @@
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F19" s="27">
         <v>0.75</v>
@@ -2495,15 +2537,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004AC3E03F954406448D57A63F810EB967" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="52e6b73825859cad1527a80b81e763dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1b05d82d297216baf5b26c55225140df">
     <xsd:element name="properties">
@@ -2617,30 +2650,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="2427474e-60f8-4f75-abfc-98841d67cf98" ContentTypeId="0x01" PreviousValue="false"/>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3772FAE1-653E-4234-8F3E-5772AF64A7BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="2427474e-60f8-4f75-abfc-98841d67cf98" ContentTypeId="0x01" PreviousValue="false"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C19439C9-4839-4823-BDE5-1DEF347CC50A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -2652,19 +2687,28 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3772FAE1-653E-4234-8F3E-5772AF64A7BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F80C0CD8-536E-4616-8B8F-E42162D98DFD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D1891D6-92B4-4639-8BA0-2F2D1A4D7AE9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F80C0CD8-536E-4616-8B8F-E42162D98DFD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>